--- a/LISTEN/Script/24_07_n3/24_07.xlsx
+++ b/LISTEN/Script/24_07_n3/24_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\24_07_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561BF742-BEFA-49B2-B223-DF775E1A3D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D465418-3F03-46F4-8140-2181F848541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19920" yWindow="330" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="330" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="198">
   <si>
     <t>Fre</t>
   </si>
@@ -333,6 +333,475 @@
   </si>
   <si>
     <t>一直；始终；远比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>閉館</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>へいかん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一時</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いちじ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏休み</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なつやすみ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鏡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かがみ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>役に立つ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>やくにたつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聴く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動き</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>うごき</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>結構</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>けっこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最初</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいしょ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>踊る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おどる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音楽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おんがく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生徒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>せいと</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中学生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高校</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>こうこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>折り紙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>おりがみ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>着る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>続く</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>つづく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>コーナー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隅，角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>アニメ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动画片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漫画</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まんが</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>貸し</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かし</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浴衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ゆかた</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>観光客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんこうきゃく</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外国人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>がいこくじん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空港</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>くうこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ことし</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飼い主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かいぬし</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>探す</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さがす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飼う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ねこ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>誘う</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さそう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>良い</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>こうどう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最終日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいしゅうび</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>親切</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しんせつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かいがい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残る</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>のこる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旅行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>りょこう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教師</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうし</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しがつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不读 よんがつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>しちがつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不读 なながつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>くがつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不读 きゅうがつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ついたち</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふつか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4日</t>
+  </si>
+  <si>
+    <t>5日</t>
+  </si>
+  <si>
+    <t>6日</t>
+  </si>
+  <si>
+    <t>7日</t>
+  </si>
+  <si>
+    <t>8日</t>
+  </si>
+  <si>
+    <t>9日</t>
+  </si>
+  <si>
+    <t>10日</t>
+  </si>
+  <si>
+    <t>みっか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>よっか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いつか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>むいか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なのか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ようか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ここのか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とおか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうよっか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>はつか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>にじゅうよっか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尾音跟着 4 号走</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうしちにち</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规（数字 + にち）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうくにち</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1442,7 +1911,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1467,142 +1936,661 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="1">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="1">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A16" s="1">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.15">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A44" s="1">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A50" s="1">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/LISTEN/Script/24_07_n3/24_07.xlsx
+++ b/LISTEN/Script/24_07_n3/24_07.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\24_07_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD48CA84-D4B6-4161-9480-E303C61F7C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C90A2F6-5088-44E6-89E6-C7F215F343F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14355" yWindow="585" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
     <sheet name="2番" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="3番" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="266">
   <si>
     <t>Fre</t>
   </si>
@@ -616,6 +616,278 @@
   </si>
   <si>
     <t>ねこ</t>
+  </si>
+  <si>
+    <t>内容</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ないよう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>関係</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんけい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指導</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しどう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蹴る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>強い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>踢；拒绝；中止</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つよい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意識</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いしき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>低く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひくく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じめん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>考える</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんがえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>動かし方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>うごかしかた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作方法；移动方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>腕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>うで</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手臂；本领，能力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿勢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しせい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>証明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうめい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>证明；证实</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>科学</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かがく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいしん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教室</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうしつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教える</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おしえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>走り方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はしりかた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特徴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とくちょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>良い点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>よいてん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>悪い点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>わるいてん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>良い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人間関係</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>にんげんかんけい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いっぽう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>趣味</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅみ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>通勤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つうきん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出勤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅっきん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大切</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たいせつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>涙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>なみだ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>笑顔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えがお</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姪っ子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>めいっこ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄色い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きいろい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -679,10 +951,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2079,10 +2354,397 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.125" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LISTEN/Script/24_07_n3/24_07.xlsx
+++ b/LISTEN/Script/24_07_n3/24_07.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\24_07_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C90A2F6-5088-44E6-89E6-C7F215F343F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349FC224-B95F-4034-BB1C-854579F49EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14355" yWindow="585" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19245" yWindow="0" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
     <sheet name="2番" sheetId="2" r:id="rId2"/>
-    <sheet name="3番" sheetId="3" r:id="rId3"/>
+    <sheet name="3番-5番" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="313">
   <si>
     <t>Fre</t>
   </si>
@@ -887,6 +887,216 @@
   </si>
   <si>
     <t>きいろい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>何かあったの</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发生什么事了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どちらでもよさそうです</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">哪个都可以 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たび</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>試合の度に</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次考试的时候</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>緊張</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きんちょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>お腹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おなか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗濯機</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財布</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいふ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>落ちる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おちる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉下；落下；坠落</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>気付</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きづけ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意；察觉；意识</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>なくす</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丢失；消除；消灭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もってくる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>带来；拿来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必ず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かならず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卒業式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そつぎょうしき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>晴れる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はれる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>祝い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いわい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>祝贺;庆祝;贺礼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いらっしゃる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「行く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・来る・いる・ある</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」等的尊敬语</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>でかける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出门;外出</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>毎回</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まいかい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>作り方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つくりかた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんたくき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おかしい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇怪；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>動く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>うごく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动；活动；运转</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -894,7 +1104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,6 +1124,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2354,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.25" style="2" customWidth="1"/>
@@ -2731,7 +2948,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
         <v>0</v>
       </c>
@@ -2740,6 +2957,260 @@
       </c>
       <c r="C33" s="2" t="s">
         <v>265</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A45" s="2">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A46" s="2">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A47" s="2">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A48" s="2">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="2">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A50" s="2">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A51" s="2">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A52" s="2">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A53" s="2">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A54" s="2">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A55" s="2">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/LISTEN/Script/24_07_n3/24_07.xlsx
+++ b/LISTEN/Script/24_07_n3/24_07.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -481,88 +481,88 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>敬語</t>
+          <t>洗剤</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>けいご</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>せんざい</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>洗涤剂;清洁剂</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>洗剤</t>
+          <t>敬語</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>せんざい</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>洗涤剂;清洁剂</t>
-        </is>
-      </c>
+          <t>けいご</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>付け</t>
+          <t>ピーマン</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>つけ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>附加；添加；附带</t>
-        </is>
-      </c>
+          <t>青椒；甜椒</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>報告</t>
+          <t>形</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ほうこく</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>かたち</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>形状；样子；形式</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>今日</t>
+          <t>報告</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>きょう</t>
+          <t>ほうこく</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -573,12 +573,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ビデオ</t>
+          <t>学ぶ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>录像；视频</t>
+          <t>まなぶ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -589,19 +589,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>割に</t>
+          <t>実際</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>わりに</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>比较；相对；意外地</t>
-        </is>
-      </c>
+          <t>じっさい</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -609,12 +605,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ピーマン</t>
+          <t>帰国</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>青椒；甜椒</t>
+          <t>きこく</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -625,12 +621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ちかちか</t>
+          <t>ビデオ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>闪烁；闪耀；刺眼</t>
+          <t>录像；视频</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -641,80 +637,84 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>形</t>
+          <t>ずっと</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>かたち</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>形状；样子；形式</t>
-        </is>
-      </c>
+          <t>一直；始终；远比</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>仕事</t>
+          <t>ちかちか</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>しごと</t>
+          <t>闪烁；闪耀；刺眼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ゴミ袋</t>
+          <t>付け</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ごみぶくろ</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>つけ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>附加；添加；附带</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>学ぶ</t>
+          <t>割に</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>まなぶ</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>わりに</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>比较；相对；意外地</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>先に</t>
+          <t>今日</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>さきに</t>
+          <t>きょう</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -725,15 +725,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>実際</t>
+          <t>載せる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>じっさい</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>のせる</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>装载；刊登</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -741,12 +745,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>出張</t>
+          <t>ビジネス</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>しゅっちょう</t>
+          <t>商业；商务</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -757,12 +761,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>急ぎ</t>
+          <t>仕事</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>いそぎ</t>
+          <t>しごと</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>帰国</t>
+          <t>ゴミ袋</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>きこく</t>
+          <t>ごみぶくろ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -789,19 +793,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>点数</t>
+          <t>先に</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>てんすう</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>分数；得分；点数</t>
-        </is>
-      </c>
+          <t>さきに</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -809,12 +809,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ビジネス</t>
+          <t>急ぎ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>商业；商务</t>
+          <t>いそぎ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -825,17 +825,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>載せる</t>
+          <t>点数</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>のせる</t>
+          <t>てんすう</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>装载；刊登</t>
+          <t>分数；得分；点数</t>
         </is>
       </c>
     </row>
@@ -845,19 +845,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>取る</t>
+          <t>出張</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>とる</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>拿取；采取；获得</t>
-        </is>
-      </c>
+          <t>しゅっちょう</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -865,19 +861,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>工夫</t>
+          <t>最後</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>くふう</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>想办法；动脑筋；钻研；窍门</t>
-        </is>
-      </c>
+          <t>さいご</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -885,15 +877,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>長い</t>
+          <t>取る</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ながい</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>とる</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>拿取；采取；获得</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -901,15 +897,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>工夫</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>せつめい</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>くふう</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>想办法；动脑筋；钻研；窍门</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -917,19 +917,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>乗せる</t>
+          <t>長い</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>のせる</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>载运；刊登；欺骗</t>
-        </is>
-      </c>
+          <t>ながい</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -937,19 +933,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>冷凍</t>
+          <t>説明</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>れいとう</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>冷冻；冷藏</t>
-        </is>
-      </c>
+          <t>せつめい</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -957,17 +949,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>お手伝い</t>
+          <t>冷凍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>おてつだい</t>
+          <t>れいとう</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>帮忙；帮助</t>
+          <t>冷冻；冷藏</t>
         </is>
       </c>
     </row>
@@ -977,15 +969,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ホストファミリー</t>
+          <t>お手伝い</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>房东家，主人家</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>おてつだい</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>帮忙；帮助</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -993,12 +989,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>最後</t>
+          <t>ホストファミリー</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>さいご</t>
+          <t>房东家，主人家</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1009,15 +1005,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ずっと</t>
+          <t>乗せる</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>一直；始终；远比</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>のせる</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>载运；刊登；欺骗</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1080,195 +1080,195 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>誘う</t>
+          <t>1日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>さそう</t>
+          <t>ついたち</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>着る</t>
+          <t>8日</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>きる</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>穿</t>
-        </is>
-      </c>
+          <t>ようか</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>飼い主</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>はつか</t>
+          <t>かいぬし</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14日</t>
+          <t>7日</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>じゅうよっか</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>尾音跟着 4 号走</t>
-        </is>
-      </c>
+          <t>なのか</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10日</t>
+          <t>17日</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>とおか</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>じゅうしちにち</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>常规（数字 + にち）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>漫画</t>
+          <t>14日</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>まんが</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>じゅうよっか</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>尾音跟着 4 号走</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17日</t>
+          <t>10日</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>じゅうしちにち</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>常规（数字 + にち）</t>
-        </is>
-      </c>
+          <t>とおか</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7日</t>
+          <t>19日</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>なのか</t>
+          <t>じゅうくにち</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>飼い主</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>かいぬし</t>
+          <t>はつか</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8日</t>
+          <t>着る</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ようか</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>きる</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>穿</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19日</t>
+          <t>3日</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>じゅうくにち</t>
+          <t>みっか</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1284,172 +1284,172 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3日</t>
+          <t>2日</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>みっか</t>
+          <t>ふつか</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2日</t>
+          <t>5日</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ふつか</t>
+          <t>いつか</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1日</t>
+          <t>7月</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ついたち</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>しちがつ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>不读 なながつ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5日</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>いつか</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>しがつ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>不读 よんがつ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7月</t>
+          <t>最終日</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>しちがつ</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>不读 なながつ</t>
-        </is>
-      </c>
+          <t>さいしゅうび</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>役に立つ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>しがつ</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>不读 よんがつ</t>
-        </is>
-      </c>
+          <t>やくにたつ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>最終日</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>さいしゅうび</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>くがつ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>不读 きゅうがつ</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>役に立つ</t>
+          <t>飼う</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>やくにたつ</t>
+          <t>かう</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>9日</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>くがつ</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>不读 きゅうがつ</t>
-        </is>
-      </c>
+          <t>ここのか</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>飼う</t>
+          <t>誘う</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>かう</t>
+          <t>さそう</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1460,92 +1460,92 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9日</t>
+          <t>踊る</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ここのか</t>
+          <t>おどる</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>踊る</t>
+          <t>行動</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>おどる</t>
+          <t>こうどう</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>空港</t>
+          <t>鏡</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>くうこう</t>
+          <t>かがみ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>探す</t>
+          <t>動き</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>さがす</t>
+          <t>うごき</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>閉館</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>こうどう</t>
+          <t>へいかん</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>動き</t>
+          <t>漫画</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>うごき</t>
+          <t>まんが</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>浴衣</t>
+          <t>一時</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ゆかた</t>
+          <t>いちじ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>親切</t>
+          <t>空港</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>しんせつ</t>
+          <t>くうこう</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>鏡</t>
+          <t>コーナー</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>かがみ</t>
+          <t>隅，角</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>閉館</t>
+          <t>教師</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>へいかん</t>
+          <t>きょうし</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1620,19 +1620,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>24日</t>
+          <t>4日</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>にじゅうよっか</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>尾音跟着 4 号走</t>
-        </is>
-      </c>
+          <t>よっか</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1640,12 +1636,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4日</t>
+          <t>聴く</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>よっか</t>
+          <t>きく</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1656,12 +1652,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>一時</t>
+          <t>海外</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>いちじ</t>
+          <t>かいがい</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1672,12 +1668,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>残る</t>
+          <t>親切</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>のこる</t>
+          <t>しんせつ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1688,12 +1684,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>今年</t>
+          <t>探す</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ことし</t>
+          <t>さがす</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1716,67 +1712,71 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>良い</t>
+          <t>浴衣</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>よい</t>
+          <t>ゆかた</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>貸し</t>
+          <t>今年</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>かし</t>
+          <t>ことし</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>続く</t>
+          <t>残る</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>つづく</t>
+          <t>のこる</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>コーナー</t>
+          <t>24日</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>隅，角</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>にじゅうよっか</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>尾音跟着 4 号走</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>アニメ</t>
+          <t>結構</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>动画片</t>
+          <t>けっこう</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>外国人</t>
+          <t>良い</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>がいこくじん</t>
+          <t>よい</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>貸し</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>けっこう</t>
+          <t>かし</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>最初</t>
+          <t>続く</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>さいしょ</t>
+          <t>つづく</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>海外</t>
+          <t>アニメ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>かいがい</t>
+          <t>动画片</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1864,19 +1864,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>生徒</t>
+          <t>音楽</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>せいと</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>中学生</t>
-        </is>
-      </c>
+          <t>おんがく</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1884,12 +1880,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>高校</t>
+          <t>最初</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>こうこう</t>
+          <t>さいしょ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1900,12 +1896,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>教師</t>
+          <t>外国人</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>きょうし</t>
+          <t>がいこくじん</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1916,15 +1912,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>旅行</t>
+          <t>生徒</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>りょこう</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>せいと</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>中学生</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>音楽</t>
+          <t>高校</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>おんがく</t>
+          <t>こうこう</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>聴く</t>
+          <t>旅行</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>きく</t>
+          <t>りょこう</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2051,127 +2051,131 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>姪っ子</t>
+          <t>関係</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>めいっこ</t>
+          <t>かんけい</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>証明</t>
+          <t>蹴る</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>しょうめい</t>
+          <t>ける</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>证明；证实</t>
+          <t>踢；拒绝；中止</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>涙</t>
+          <t>でかける</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>なみだ</t>
+          <t>出门;外出</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>姿勢</t>
+          <t>姪っ子</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>しせい</t>
+          <t>めいっこ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>地面</t>
+          <t>証明</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>じめん</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>しょうめい</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>证明；证实</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>でかける</t>
+          <t>祝い</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>出门;外出</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>いわい</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>祝贺;庆祝;贺礼</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>祝い</t>
+          <t>姿勢</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>いわい</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>祝贺;庆祝;贺礼</t>
-        </is>
-      </c>
+          <t>しせい</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2191,27 +2195,23 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>蹴る</t>
+          <t>涙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ける</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>踢；拒绝；中止</t>
-        </is>
-      </c>
+          <t>なみだ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2227,87 +2227,91 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>お腹</t>
+          <t>特徴</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>おなか</t>
+          <t>とくちょう</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>特徴</t>
+          <t>試合の度に</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>とくちょう</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>たび</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>每次考试的时候</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>関係</t>
+          <t>洗濯機</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>かんけい</t>
+          <t>せんたくき</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>試合の度に</t>
+          <t>緊張</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>たび</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>每次考试的时候</t>
-        </is>
-      </c>
+          <t>きんちょう</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>緊張</t>
+          <t>動く</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>きんちょう</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>うごく</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>移动；活动；运转</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2315,19 +2319,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>動く</t>
+          <t>お腹</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>うごく</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>移动；活动；运转</t>
-        </is>
-      </c>
+          <t>おなか</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2335,83 +2335,83 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>洗濯機</t>
+          <t>科学</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>せんたくき</t>
+          <t>かがく</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>教える</t>
+          <t>人間関係</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>おしえる</t>
+          <t>にんげんかんけい</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>最新</t>
+          <t>もってくる</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>さいしん</t>
+          <t>带来；拿来</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科学</t>
+          <t>良い点</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>かがく</t>
+          <t>よいてん</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>指導</t>
+          <t>地面</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>しどう</t>
+          <t>じめん</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2435,19 +2435,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>走り方</t>
+          <t>財布</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>はしりかた</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>跑步方式</t>
-        </is>
-      </c>
+          <t>さいふ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2471,12 +2467,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>出勤</t>
+          <t>教える</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>しゅっきん</t>
+          <t>おしえる</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2487,12 +2483,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>黄色い</t>
+          <t>最新</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>きいろい</t>
+          <t>さいしん</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2503,15 +2499,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>良い点</t>
+          <t>走り方</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>よいてん</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>はしりかた</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>跑步方式</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>良い</t>
+          <t>指導</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>いい</t>
+          <t>しどう</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2535,15 +2535,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>何かあったの</t>
+          <t>気付</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>发生什么事了</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>きづけ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>注意；察觉；意识</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2551,12 +2555,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>一方</t>
+          <t>出勤</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>いっぽう</t>
+          <t>しゅっきん</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2599,12 +2603,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>人間関係</t>
+          <t>黄色い</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>にんげんかんけい</t>
+          <t>きいろい</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2615,12 +2619,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>もってくる</t>
+          <t>大切</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>带来；拿来</t>
+          <t>たいせつ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2631,48 +2635,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>気付</t>
+          <t>一方</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>きづけ</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>注意；察觉；意识</t>
-        </is>
-      </c>
+          <t>いっぽう</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>財布</t>
+          <t>良い</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>さいふ</t>
+          <t>いい</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>悪い点</t>
+          <t>何かあったの</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>わるいてん</t>
+          <t>发生什么事了</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>毎回</t>
+          <t>強い</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>まいかい</t>
+          <t>つよい</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>教室</t>
+          <t>悪い点</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>きょうしつ</t>
+          <t>わるいてん</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>趣味</t>
+          <t>毎回</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>しゅみ</t>
+          <t>まいかい</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>作り方</t>
+          <t>教室</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>つくりかた</t>
+          <t>きょうしつ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2747,19 +2747,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>落ちる</t>
+          <t>作り方</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>おちる</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>掉下；落下；坠落</t>
-        </is>
-      </c>
+          <t>つくりかた</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2767,15 +2763,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>強い</t>
+          <t>落ちる</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>つよい</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>おちる</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>掉下；落下；坠落</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>どちらでもよさそうです</t>
+          <t>趣味</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">哪个都可以 </t>
+          <t>しゅみ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>考える</t>
+          <t>どちらでもよさそうです</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>かんがえる</t>
+          <t xml:space="preserve">哪个都可以 </t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>考える</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>丢失；消除；消灭</t>
+          <t>かんがえる</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>低く</t>
+          <t>なくす</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ひくく</t>
+          <t>丢失；消除；消灭</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>大切</t>
+          <t>低く</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>たいせつ</t>
+          <t>ひくく</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
